--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>354_雾中情人_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020100</v>
+        <v>03010103030301020101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -521,7 +521,7 @@
         <v>354_雾中情人_undefined_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -581,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101</v>
+        <v>030101030303010201010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>560_橙菠萝_Safflower_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101030303010201010</v>
+        <v>03010103030301020101051551010201010150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010150</v>
+        <v>030101030303010201010515510102010101510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>3</v>
+      </c>
+      <c r="C23" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>4</v>
+      </c>
+      <c r="C28" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101030303010201010515510102010101510</v>
+        <v>03010103030301020101051551010201010151010139.5109158680</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>626_多丁莫言_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.5109158680</v>
+        <v>03010103030301020101051551010201010151010139.5109158681</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -690,12 +690,92 @@
         <v>626_多丁莫言_undefined_undefined_1bunch</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>5</v>
+      </c>
+      <c r="C34" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>361_小天使鹅掌芋_Thaumatophyllum xanadu_Thaumatophyllum xanadu_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.5109158681</v>
+        <v>03010103030301020101051551010201010151010139.5109158681010101055516550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -770,7 +770,7 @@
     </row>
     <row r="41">
       <c r="C41" t="str">
-        <v>361_小天使鹅掌芋_Thaumatophyllum xanadu_Thaumatophyllum xanadu_1bunch</v>
+        <v>609_康乃馨小天使_angle_undefined_20stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -772,6 +772,9 @@
       <c r="C41" t="str">
         <v>609_康乃馨小天使_angle_undefined_20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -830,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.5109158681010101055516550</v>
+        <v>03010103030301020101051551010201010151010139.5109158681010101055516555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,95 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v>65_白月光_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6</v>
+      </c>
+      <c r="C46" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v>79_福娃_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>900_紫罗兰深紫_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -833,7 +919,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.5109158681010101055516555</v>
+        <v>03010103030301020101051551010201010151010139.51091586810101010555165551510510751020100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -861,6 +861,9 @@
       <c r="C51" t="str">
         <v>900_紫罗兰深紫_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -919,7 +922,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.51091586810101010555165551510510751020100</v>
+        <v>03010103030301020101051551010201010151010139.51091586810101010555165551510510751020105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -865,9 +865,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>899_紫罗兰浅黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>7</v>
+      </c>
+      <c r="C59" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>780_贝壳草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -922,7 +1002,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.51091586810101010555165551510510751020105</v>
+        <v>03010103030301020101051551010201010151010139.510915868101010105551655515105107510201052055103522050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -944,6 +944,9 @@
       <c r="C61" t="str">
         <v>771_美洲茶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1002,7 +1005,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.510915868101010105551655515105107510201052055103522050</v>
+        <v>03010103030301020101051551010201010151010139.510915868101010105551655515105107510201052055103522057</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -948,9 +948,66 @@
         <v>7</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>770_小弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>8</v>
+      </c>
+      <c r="C64" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>9</v>
+      </c>
+      <c r="C66" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>10</v>
+      </c>
+      <c r="C67" t="str">
+        <v>836_胡姬兰紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L67"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1005,7 +1062,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010103030301020101051551010201010151010139.510915868101010105551655515105107510201052055103522057</v>
+        <v>03010103030301020101051551010201010151010139.5109158681010101055516555151051075102010520551035220571510101035</v>
       </c>
     </row>
   </sheetData>
